--- a/survey_templates/032_employee_monthly_feedback_form--survey_templates.xlsx
+++ b/survey_templates/032_employee_monthly_feedback_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Employee Name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This form is for employee feedback and satisfaction on their job.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>job_satisfaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Overall Job Satisfaction</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How would you rate your overall job satisfaction?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Job Title</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Which department do you belong to?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,17 +596,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>job_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Available Work Hours</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +624,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work_hours</t>
+          <t>job_satisfaction_level</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Work Hours</t>
+          <t>Specific Job Satisfaction</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +642,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>submission_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salary</t>
+          <t>Feedback Frequency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +665,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Submission Date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +693,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>job_satisfaction_level</t>
+          <t>assigned_to</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Job Satisfaction Level</t>
+          <t>Assigned To</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +711,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>feedback_frequency</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Feedback Frequency</t>
+          <t>Submitted By</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +734,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +757,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>feedback_frequency_frequency</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Feedback Frequency</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +780,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Assigned To</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,297 +803,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submission_date_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submission Date 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>work_hours_1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Work Hours</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>work_hours_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Work Hours</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>work_hours_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Work Hours</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>work_hours_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Work Hours</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>work_hours_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Work Hours</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submission_date_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submission Date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submission_date_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submission Date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submission_date_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submission Date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submission_date_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submission Date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission_date_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submission Date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +834,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1131,12 +867,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +884,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1165,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1182,12 +918,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1199,19 +935,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>highly_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Highly Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>job_hours_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +964,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>job_hours_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +981,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>job_hours_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +998,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>job_hours_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1015,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>work_hours_choices</t>
+          <t>job_hours_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1301,12 +1037,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>highly_satisfied</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Highly Satisfied</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1054,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1071,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1088,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1369,641 +1105,165 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>highly_dissatisfied</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Highly Dissatisfied</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>submission_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>submission_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bi-annual</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>submission_frequency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>bi-annual</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>Bi-Annual</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>feedback_frequency_frequency_choices</t>
+          <t>submission_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>feedback_frequency_frequency_choices</t>
+          <t>assigned_to_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>feedback_frequency_frequency_choices</t>
+          <t>assigned_to_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bi-annual</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bi-Annual</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>feedback_frequency_frequency_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>employee_a</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>Employee A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>employee_b</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Employee B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>employee_c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>submitted_by_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>employee_a</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Employee A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>submitted_by_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>employee_b</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Employee B</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>submitted_by_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>employee_c</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>Employee C</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>work_hours_1_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>8am_-_5pm</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>8am - 5pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>work_hours_1_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>9am_-_6pm</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>9am - 6pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>work_hours_1_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>10am_-_7pm</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>10am - 7pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>work_hours_1_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>11am_-_8pm</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>11am - 8pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>work_hours_1_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>12pm_-_9pm</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>12pm - 9pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>work_hours_2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>8am_-_5pm</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>8am - 5pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>work_hours_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>9am_-_6pm</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>9am - 6pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>work_hours_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>10am_-_7pm</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>10am - 7pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>work_hours_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>11am_-_8pm</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>11am - 8pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>work_hours_2_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>12pm_-_9pm</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>12pm - 9pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>work_hours_3_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>8am_-_5pm</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>8am - 5pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>work_hours_3_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>9am_-_6pm</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>9am - 6pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>work_hours_3_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10am_-_7pm</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>10am - 7pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>work_hours_3_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>11am_-_8pm</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>11am - 8pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>work_hours_3_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>12pm_-_9pm</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>12pm - 9pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>work_hours_4_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>8am_-_5pm</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>8am - 5pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>work_hours_4_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>9am_-_6pm</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>9am - 6pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>work_hours_4_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>10am_-_7pm</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>10am - 7pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>work_hours_4_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>11am_-_8pm</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>11am - 8pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>work_hours_4_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>12pm_-_9pm</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>12pm - 9pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>work_hours_5_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>8am_-_5pm</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>8am - 5pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>work_hours_5_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>9am_-_6pm</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>9am - 6pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>work_hours_5_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>10am_-_7pm</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>10am - 7pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>work_hours_5_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>11am_-_8pm</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>11am - 8pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>work_hours_5_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>12pm_-_9pm</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>12pm - 9pm</t>
         </is>
       </c>
     </row>
